--- a/data/Comparación de Venta Diaria por SKU.xlsx
+++ b/data/Comparación de Venta Diaria por SKU.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D915E756-44B4-4E73-9BCF-8F9FA5D47FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{0E5779F7-8682-44DE-88C6-83F206C2BBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -233,14 +233,22 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -269,8 +277,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,6 +302,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -314,30 +335,66 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="20">
+    <cellStyle name="Bueno 2" xfId="9" xr:uid="{94F67CAC-752E-4491-A3E3-C4BB62743B72}"/>
+    <cellStyle name="Bueno 3" xfId="13" xr:uid="{4F709AEB-99D0-454B-A65A-29BEAE46F7D3}"/>
+    <cellStyle name="Bueno 4" xfId="19" xr:uid="{CB352053-6C19-43CD-B03E-627D0A7258B8}"/>
+    <cellStyle name="Millares 2" xfId="5" xr:uid="{2375C8DF-BDBA-43D5-9D31-543C4EE04C41}"/>
+    <cellStyle name="Millares 3" xfId="7" xr:uid="{27A5BDA4-BEC6-4D39-8EC6-81077DACAD2E}"/>
+    <cellStyle name="Millares 4" xfId="11" xr:uid="{A8866BDA-94C2-4640-AEC3-761F4953E7A9}"/>
+    <cellStyle name="Millares 5" xfId="14" xr:uid="{259FBDCB-E288-4DE6-A5A1-D75AC9203F66}"/>
+    <cellStyle name="Millares 6" xfId="15" xr:uid="{EBD22DEF-DD97-40DE-9E0D-75DB84FC7626}"/>
+    <cellStyle name="Millares 7" xfId="17" xr:uid="{5D7A9A1C-84A4-48A0-B651-270D23CCD661}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6A46E9E3-F881-4AFA-9613-5EAED1E58279}"/>
+    <cellStyle name="Normal 2 2" xfId="4" xr:uid="{B06DF990-D905-408E-BFA0-44405515E01D}"/>
+    <cellStyle name="Normal 3" xfId="6" xr:uid="{3CC58EFF-C4E0-4F85-B088-2FDD0B926453}"/>
+    <cellStyle name="Normal 4" xfId="10" xr:uid="{0DD17921-2CD6-422C-A23C-9A67FFB24691}"/>
+    <cellStyle name="Normal 5" xfId="16" xr:uid="{6D56047B-2B25-4585-8E22-6D9FFAE9B0FE}"/>
+    <cellStyle name="Normal 6" xfId="2" xr:uid="{13ADE74A-2259-43F4-9CA9-C254DDCD9F7C}"/>
+    <cellStyle name="Porcentaje 2" xfId="8" xr:uid="{9BC1E1EC-552B-4A61-AC7B-93A66CA2C63A}"/>
+    <cellStyle name="Porcentaje 3" xfId="12" xr:uid="{1BCE6996-3CD8-414B-A94D-1F5613AF54F4}"/>
+    <cellStyle name="Porcentaje 4" xfId="18" xr:uid="{12FA4737-A541-4FD6-B499-94C89E1AA6CA}"/>
+    <cellStyle name="Porcentaje 5" xfId="3" xr:uid="{03AE4CCC-FE99-48B8-A7EC-56272B60C026}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -354,545 +411,455 @@
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="INVENTARIO NACIONAL 01-10-26"/>
-      <sheetName val="INVENTARIO NACIONAL 02-10-26"/>
-      <sheetName val="CCC"/>
-      <sheetName val="VINCULO VTS BY SKU SEPTIEMBRE"/>
-      <sheetName val="VINCULO VTS BY SKU OPEN"/>
-      <sheetName val="DESV. VTS BY SKU"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
-        <row r="4">
-          <cell r="F4">
-            <v>770</v>
-          </cell>
-          <cell r="G4">
-            <v>-0.36389921520033042</v>
-          </cell>
-          <cell r="H4" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="F5">
-            <v>0</v>
-          </cell>
-          <cell r="G5">
-            <v>-1</v>
-          </cell>
-          <cell r="H5" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="F6">
-            <v>380</v>
-          </cell>
-          <cell r="G6">
-            <v>-0.23239371958497845</v>
-          </cell>
-          <cell r="H6" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="F7">
-            <v>56</v>
-          </cell>
-          <cell r="G7">
-            <v>-0.4925864909390445</v>
-          </cell>
-          <cell r="H7" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="F8">
-            <v>2</v>
-          </cell>
-          <cell r="G8">
-            <v>-0.86746987951807231</v>
-          </cell>
-          <cell r="H8" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="F9">
-            <v>1256</v>
-          </cell>
-          <cell r="G9">
-            <v>-0.11208226221079687</v>
-          </cell>
-          <cell r="H9" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="F10">
-            <v>108</v>
-          </cell>
-          <cell r="G10">
-            <v>-0.28627215379993987</v>
-          </cell>
-          <cell r="H10" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="F11">
-            <v>231</v>
-          </cell>
-          <cell r="G11">
-            <v>-0.3065902578796561</v>
-          </cell>
-          <cell r="H11" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="F12">
-            <v>450</v>
-          </cell>
-          <cell r="G12">
-            <v>-0.44782196441519329</v>
-          </cell>
-          <cell r="H12" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="F13">
-            <v>220</v>
-          </cell>
-          <cell r="G13">
-            <v>-0.45174444947893067</v>
-          </cell>
-          <cell r="H13" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="F14">
-            <v>2663</v>
-          </cell>
-          <cell r="G14">
-            <v>-0.22616861931870724</v>
-          </cell>
-          <cell r="H14" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="F15">
-            <v>1618</v>
-          </cell>
-          <cell r="G15">
-            <v>-0.25172899455550657</v>
-          </cell>
-          <cell r="H15" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="F16">
-            <v>1602</v>
-          </cell>
-          <cell r="G16">
-            <v>-0.26238462987379929</v>
-          </cell>
-          <cell r="H16" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="F17">
-            <v>2030</v>
-          </cell>
-          <cell r="G17">
-            <v>-0.23955796965723919</v>
-          </cell>
-          <cell r="H17" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="F18">
-            <v>552</v>
-          </cell>
-          <cell r="G18">
-            <v>-0.24392977213298472</v>
-          </cell>
-          <cell r="H18" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="F19">
-            <v>687</v>
-          </cell>
-          <cell r="G19">
-            <v>-0.21477556109725682</v>
-          </cell>
-          <cell r="H19" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="F20">
-            <v>646</v>
-          </cell>
-          <cell r="G20">
-            <v>-0.25816891115982887</v>
-          </cell>
-          <cell r="H20" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="F21">
-            <v>151</v>
-          </cell>
-          <cell r="G21">
-            <v>-0.46771350745072904</v>
-          </cell>
-          <cell r="H21" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="F22">
-            <v>52</v>
-          </cell>
-          <cell r="G22">
-            <v>-0.63694065376071085</v>
-          </cell>
-          <cell r="H22" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="F23">
-            <v>287</v>
-          </cell>
-          <cell r="G23">
-            <v>-0.45347528780403357</v>
-          </cell>
-          <cell r="H23" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="F24">
-            <v>463</v>
-          </cell>
-          <cell r="G24">
-            <v>-0.48370419179887469</v>
-          </cell>
-          <cell r="H24" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="F25">
-            <v>0</v>
-          </cell>
-          <cell r="G25">
-            <v>-1</v>
-          </cell>
-          <cell r="H25" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="F26">
-            <v>440</v>
-          </cell>
-          <cell r="G26">
-            <v>-0.38590369853454287</v>
-          </cell>
-          <cell r="H26" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="F27">
-            <v>954</v>
-          </cell>
-          <cell r="G27">
-            <v>-0.13785737758790662</v>
-          </cell>
-          <cell r="H27" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="F28">
-            <v>284</v>
-          </cell>
-          <cell r="G28">
-            <v>-0.51290247134949718</v>
-          </cell>
-          <cell r="H28" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="F29">
-            <v>243</v>
-          </cell>
-          <cell r="G29">
-            <v>-0.4871942446043166</v>
-          </cell>
-          <cell r="H29" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="F30">
-            <v>339</v>
-          </cell>
-          <cell r="G30">
-            <v>0.34184958618207983</v>
-          </cell>
-          <cell r="H30" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="F31">
-            <v>361</v>
-          </cell>
-          <cell r="G31">
-            <v>0.16897262290256121</v>
-          </cell>
-          <cell r="H31" t="str">
-            <v>SUBIÓ</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="F32">
-            <v>55</v>
-          </cell>
-          <cell r="G32">
-            <v>-0.60079181788188718</v>
-          </cell>
-          <cell r="H32" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="F33">
-            <v>80</v>
-          </cell>
-          <cell r="G33">
-            <v>-0.47446999104210208</v>
-          </cell>
-          <cell r="H33" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="F34">
-            <v>561</v>
-          </cell>
-          <cell r="G34">
-            <v>-0.31736725663716814</v>
-          </cell>
-          <cell r="H34" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="F35">
-            <v>339</v>
-          </cell>
-          <cell r="G35">
-            <v>-0.46093241778099026</v>
-          </cell>
-          <cell r="H35" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="F36">
-            <v>498</v>
-          </cell>
-          <cell r="G36">
-            <v>-0.39888071985076268</v>
-          </cell>
-          <cell r="H36" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="F37">
-            <v>351</v>
-          </cell>
-          <cell r="G37">
-            <v>-0.36627000410340582</v>
-          </cell>
-          <cell r="H37" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="F38">
-            <v>1</v>
-          </cell>
-          <cell r="G38">
-            <v>-0.73170731707317072</v>
-          </cell>
-          <cell r="H38" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="F39">
-            <v>0</v>
-          </cell>
-          <cell r="G39">
-            <v>-1</v>
-          </cell>
-          <cell r="H39" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="F40">
-            <v>56</v>
-          </cell>
-          <cell r="G40">
-            <v>-0.55085672621217641</v>
-          </cell>
-          <cell r="H40" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="F41">
-            <v>371</v>
-          </cell>
-          <cell r="G41">
-            <v>-0.38455738199366618</v>
-          </cell>
-          <cell r="H41" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="F42">
-            <v>342</v>
-          </cell>
-          <cell r="G42">
-            <v>-0.20624538453423358</v>
-          </cell>
-          <cell r="H42" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="F43">
-            <v>202</v>
-          </cell>
-          <cell r="G43">
-            <v>-0.26859776168531935</v>
-          </cell>
-          <cell r="H43" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="F44">
-            <v>330</v>
-          </cell>
-          <cell r="G44">
-            <v>-0.35207496653279791</v>
-          </cell>
-          <cell r="H44" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="F45">
-            <v>151</v>
-          </cell>
-          <cell r="G45">
-            <v>-0.52657830981901088</v>
-          </cell>
-          <cell r="H45" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="F46">
-            <v>216</v>
-          </cell>
-          <cell r="G46">
-            <v>-0.28957990731050987</v>
-          </cell>
-          <cell r="H46" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="F47">
-            <v>16</v>
-          </cell>
-          <cell r="G47">
-            <v>-0.73474001507159004</v>
-          </cell>
-          <cell r="H47" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="F48">
-            <v>24</v>
-          </cell>
-          <cell r="G48">
-            <v>-0.79613899613899619</v>
-          </cell>
-          <cell r="H48" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="F49">
-            <v>12</v>
-          </cell>
-          <cell r="G49">
-            <v>-0.70989010989010992</v>
-          </cell>
-          <cell r="H49" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="F50">
-            <v>16</v>
-          </cell>
-          <cell r="G50">
-            <v>-0.68058076225045372</v>
-          </cell>
-          <cell r="H50" t="str">
-            <v>BAJO</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
+  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
+    <oleItems>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!DESV. VTS BY SKU!F4C6:F50C6" advise="1">
+            <x14:values rows="47">
+              <value>
+                <val>1379.5</val>
+              </value>
+              <value>
+                <val>1.5</val>
+              </value>
+              <value>
+                <val>622</val>
+              </value>
+              <value>
+                <val>86.5</val>
+              </value>
+              <value>
+                <val>8.5</val>
+              </value>
+              <value>
+                <val>2007</val>
+              </value>
+              <value>
+                <val>211</val>
+              </value>
+              <value>
+                <val>445.5</val>
+              </value>
+              <value>
+                <val>824.5</val>
+              </value>
+              <value>
+                <val>334</val>
+              </value>
+              <value>
+                <val>3894.5</val>
+              </value>
+              <value>
+                <val>2513.5</val>
+              </value>
+              <value>
+                <val>2404</val>
+              </value>
+              <value>
+                <val>2877</val>
+              </value>
+              <value>
+                <val>775</val>
+              </value>
+              <value>
+                <val>1050</val>
+              </value>
+              <value>
+                <val>1029</val>
+              </value>
+              <value>
+                <val>208</val>
+              </value>
+              <value>
+                <val>99</val>
+              </value>
+              <value>
+                <val>461</val>
+              </value>
+              <value>
+                <val>796</val>
+              </value>
+              <value>
+                <val>130</val>
+              </value>
+              <value>
+                <val>777</val>
+              </value>
+              <value>
+                <val>1322.5</val>
+              </value>
+              <value>
+                <val>566.5</val>
+              </value>
+              <value>
+                <val>513</val>
+              </value>
+              <value>
+                <val>395</val>
+              </value>
+              <value>
+                <val>510</val>
+              </value>
+              <value>
+                <val>77</val>
+              </value>
+              <value>
+                <val>149</val>
+              </value>
+              <value>
+                <val>958</val>
+              </value>
+              <value>
+                <val>655</val>
+              </value>
+              <value>
+                <val>873</val>
+              </value>
+              <value>
+                <val>585.5</val>
+              </value>
+              <value>
+                <val>3</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>60</val>
+              </value>
+              <value>
+                <val>618.5</val>
+              </value>
+              <value>
+                <val>460</val>
+              </value>
+              <value>
+                <val>310</val>
+              </value>
+              <value>
+                <val>575</val>
+              </value>
+              <value>
+                <val>292</val>
+              </value>
+              <value>
+                <val>316</val>
+              </value>
+              <value>
+                <val>31.5</val>
+              </value>
+              <value>
+                <val>65</val>
+              </value>
+              <value>
+                <val>25.5</val>
+              </value>
+              <value>
+                <val>34</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!DESV. VTS BY SKU!F4C6:F50C6" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!DESV. VTS BY SKU!F4C7:F50C8" advise="1">
+            <x14:values rows="47" cols="2">
+              <value>
+                <val>0.13961173068979771</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>-0.96529968454258674</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>0.25645028004774573</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>-0.21622734761120266</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>-0.43674698795180722</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>0.4188303341902313</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>0.39441273655752473</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>0.3372902169463774</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>1.1712867421495909E-2</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>-0.16764839148164923</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>0.13168843862684754</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>0.16240987156040432</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>0.10688348925305036</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>7.7729911968533516E-2</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>6.1511642385755128E-2</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>0.20012468827930174</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>0.18164735358596928</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>-0.26678416920365322</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>-0.30879086004443035</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>-0.12213277936466715</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>-0.11237264939936131</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>0.98611111111111116</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>8.4438241451500362E-2</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>0.19516102530397639</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>-2.8377640913697655E-2</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>8.2589928057553941E-2</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>0.5635120546959338</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>0.65145716808949072</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>-0.44110854503464203</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>-2.1200358315915158E-2</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>0.16570796460176984</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>4.1561257679797681E-2</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>5.3769340502578755E-2</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>5.7119409109560815E-2</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>-0.19512195121951215</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>-1</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>-0.51877506379876048</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>2.6014175840747944E-2</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>6.7623167000738338E-2</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>0.12244897959183665</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>0.12896028558679151</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>-8.4509049451332419E-2</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>3.9318283749439242E-2</val>
+              </value>
+              <value t="str">
+                <val>SUBIÓ</val>
+              </value>
+              <value>
+                <val>-0.47776940467219298</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>-0.44787644787644787</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>-0.3835164835164836</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+              <value>
+                <val>-0.32123411978221417</val>
+              </value>
+              <value t="str">
+                <val>BAJO</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!DESV. VTS BY SKU!F4C7:F50C8" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </oleItems>
+  </oleLink>
 </externalLink>
 </file>
 
@@ -1095,18 +1062,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
-    <col min="6" max="8" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" customWidth="1"/>
+    <col min="6" max="8" width="17.6640625" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1132,7 +1099,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>110150</v>
       </c>
@@ -1146,22 +1113,22 @@
         <v>1210.5</v>
       </c>
       <c r="E2" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>770</v>
+        <f t="array" aca="1" ref="E2:E48" ca="1">[1]!'!DESV. VTS BY SKU!F4C6:F50C6'</f>
+        <v>1379.5</v>
       </c>
       <c r="F2" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-0.36389921520033042</v>
+        <f t="array" aca="1" ref="F2:G48" ca="1">[1]!'!DESV. VTS BY SKU!F4C7:F50C8'</f>
+        <v>0.13961173068979771</v>
       </c>
       <c r="G2" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H2">
         <v>1.36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>110151</v>
       </c>
@@ -1175,22 +1142,22 @@
         <v>43.227272727272727</v>
       </c>
       <c r="E3" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>0</v>
+        <f ca="1"/>
+        <v>1.5</v>
       </c>
       <c r="F3" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-1</v>
+        <f ca="1"/>
+        <v>-0.96529968454258674</v>
       </c>
       <c r="G3" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H3">
         <v>1.59</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>110230</v>
       </c>
@@ -1204,22 +1171,22 @@
         <v>495.04545454545456</v>
       </c>
       <c r="E4" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>380</v>
+        <f ca="1"/>
+        <v>622</v>
       </c>
       <c r="F4" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.23239371958497845</v>
+        <f ca="1"/>
+        <v>0.25645028004774573</v>
       </c>
       <c r="G4" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H4">
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>110400</v>
       </c>
@@ -1233,22 +1200,22 @@
         <v>110.36363636363636</v>
       </c>
       <c r="E5" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>56</v>
+        <f ca="1"/>
+        <v>86.5</v>
       </c>
       <c r="F5" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-0.4925864909390445</v>
+        <f ca="1"/>
+        <v>-0.21622734761120266</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H5">
         <v>3.61</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>111000</v>
       </c>
@@ -1262,22 +1229,22 @@
         <v>15.090909090909092</v>
       </c>
       <c r="E6" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>2</v>
+        <f ca="1"/>
+        <v>8.5</v>
       </c>
       <c r="F6" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.86746987951807231</v>
+        <f ca="1"/>
+        <v>-0.43674698795180722</v>
       </c>
       <c r="G6" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H6">
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>120130</v>
       </c>
@@ -1291,22 +1258,22 @@
         <v>1414.5454545454545</v>
       </c>
       <c r="E7" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1256</v>
+        <f ca="1"/>
+        <v>2007</v>
       </c>
       <c r="F7" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>-0.11208226221079687</v>
+        <f ca="1"/>
+        <v>0.4188303341902313</v>
       </c>
       <c r="G7" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H7">
         <v>0.63</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>120131</v>
       </c>
@@ -1320,22 +1287,22 @@
         <v>151.31818181818181</v>
       </c>
       <c r="E8" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>108</v>
+        <f ca="1"/>
+        <v>211</v>
       </c>
       <c r="F8" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.28627215379993987</v>
+        <f ca="1"/>
+        <v>0.39441273655752473</v>
       </c>
       <c r="G8" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H8">
         <v>0.63</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>120132</v>
       </c>
@@ -1349,22 +1316,22 @@
         <v>333.13636363636363</v>
       </c>
       <c r="E9" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>231</v>
+        <f ca="1"/>
+        <v>445.5</v>
       </c>
       <c r="F9" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.3065902578796561</v>
+        <f ca="1"/>
+        <v>0.3372902169463774</v>
       </c>
       <c r="G9" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H9">
         <v>0.63</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>130150</v>
       </c>
@@ -1378,22 +1345,22 @@
         <v>814.9545454545455</v>
       </c>
       <c r="E10" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>450</v>
+        <f ca="1"/>
+        <v>824.5</v>
       </c>
       <c r="F10" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.44782196441519329</v>
+        <f ca="1"/>
+        <v>1.1712867421495909E-2</v>
       </c>
       <c r="G10" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H10">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>130151</v>
       </c>
@@ -1407,22 +1374,22 @@
         <v>401.27272727272725</v>
       </c>
       <c r="E11" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>220</v>
+        <f ca="1"/>
+        <v>334</v>
       </c>
       <c r="F11" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.45174444947893067</v>
+        <f ca="1"/>
+        <v>-0.16764839148164923</v>
       </c>
       <c r="G11" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H11">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>130152</v>
       </c>
@@ -1436,22 +1403,22 @@
         <v>3441.318181818182</v>
       </c>
       <c r="E12" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>2663</v>
+        <f ca="1"/>
+        <v>3894.5</v>
       </c>
       <c r="F12" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.22616861931870724</v>
+        <f ca="1"/>
+        <v>0.13168843862684754</v>
       </c>
       <c r="G12" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H12">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>130153</v>
       </c>
@@ -1465,22 +1432,22 @@
         <v>2162.318181818182</v>
       </c>
       <c r="E13" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1618</v>
+        <f ca="1"/>
+        <v>2513.5</v>
       </c>
       <c r="F13" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.25172899455550657</v>
+        <f ca="1"/>
+        <v>0.16240987156040432</v>
       </c>
       <c r="G13" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H13">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>130154</v>
       </c>
@@ -1494,22 +1461,22 @@
         <v>2171.8636363636365</v>
       </c>
       <c r="E14" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>1602</v>
+        <f ca="1"/>
+        <v>2404</v>
       </c>
       <c r="F14" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.26238462987379929</v>
+        <f ca="1"/>
+        <v>0.10688348925305036</v>
       </c>
       <c r="G14" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H14">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>130155</v>
       </c>
@@ -1523,22 +1490,22 @@
         <v>2669.5</v>
       </c>
       <c r="E15" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2030</v>
+        <f ca="1"/>
+        <v>2877</v>
       </c>
       <c r="F15" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.23955796965723919</v>
+        <f ca="1"/>
+        <v>7.7729911968533516E-2</v>
       </c>
       <c r="G15" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H15">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>130157</v>
       </c>
@@ -1552,22 +1519,22 @@
         <v>730.09090909090912</v>
       </c>
       <c r="E16" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>552</v>
+        <f ca="1"/>
+        <v>775</v>
       </c>
       <c r="F16" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.24392977213298472</v>
+        <f ca="1"/>
+        <v>6.1511642385755128E-2</v>
       </c>
       <c r="G16" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H16">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>130158</v>
       </c>
@@ -1581,22 +1548,22 @@
         <v>874.90909090909088</v>
       </c>
       <c r="E17" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>687</v>
+        <f ca="1"/>
+        <v>1050</v>
       </c>
       <c r="F17" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-0.21477556109725682</v>
+        <f ca="1"/>
+        <v>0.20012468827930174</v>
       </c>
       <c r="G17" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H17">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>130159</v>
       </c>
@@ -1610,22 +1577,22 @@
         <v>870.81818181818187</v>
       </c>
       <c r="E18" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>646</v>
+        <f ca="1"/>
+        <v>1029</v>
       </c>
       <c r="F18" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.25816891115982887</v>
+        <f ca="1"/>
+        <v>0.18164735358596928</v>
       </c>
       <c r="G18" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H18">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>130700</v>
       </c>
@@ -1639,22 +1606,22 @@
         <v>283.68181818181819</v>
       </c>
       <c r="E19" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>151</v>
+        <f ca="1"/>
+        <v>208</v>
       </c>
       <c r="F19" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-0.46771350745072904</v>
+        <f ca="1"/>
+        <v>-0.26678416920365322</v>
       </c>
       <c r="G19" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H19">
         <v>3.68</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>130701</v>
       </c>
@@ -1668,22 +1635,22 @@
         <v>143.22727272727272</v>
       </c>
       <c r="E20" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>52</v>
+        <f ca="1"/>
+        <v>99</v>
       </c>
       <c r="F20" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.63694065376071085</v>
+        <f ca="1"/>
+        <v>-0.30879086004443035</v>
       </c>
       <c r="G20" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H20">
         <v>3.68</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>130702</v>
       </c>
@@ -1697,22 +1664,22 @@
         <v>525.13636363636363</v>
       </c>
       <c r="E21" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>287</v>
+        <f ca="1"/>
+        <v>461</v>
       </c>
       <c r="F21" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-0.45347528780403357</v>
+        <f ca="1"/>
+        <v>-0.12213277936466715</v>
       </c>
       <c r="G21" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>130703</v>
       </c>
@@ -1726,22 +1693,22 @@
         <v>896.77272727272725</v>
       </c>
       <c r="E22" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>463</v>
+        <f ca="1"/>
+        <v>796</v>
       </c>
       <c r="F22" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>-0.48370419179887469</v>
+        <f ca="1"/>
+        <v>-0.11237264939936131</v>
       </c>
       <c r="G22" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>130707</v>
       </c>
@@ -1755,22 +1722,22 @@
         <v>65.454545454545453</v>
       </c>
       <c r="E23" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>0</v>
+        <f ca="1"/>
+        <v>130</v>
       </c>
       <c r="F23" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-1</v>
+        <f ca="1"/>
+        <v>0.98611111111111116</v>
       </c>
       <c r="G23" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H23">
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>131150</v>
       </c>
@@ -1784,22 +1751,22 @@
         <v>716.5</v>
       </c>
       <c r="E24" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>440</v>
+        <f ca="1"/>
+        <v>777</v>
       </c>
       <c r="F24" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.38590369853454287</v>
+        <f ca="1"/>
+        <v>8.4438241451500362E-2</v>
       </c>
       <c r="G24" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H24">
         <v>1.63</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>131151</v>
       </c>
@@ -1813,22 +1780,22 @@
         <v>1106.5454545454545</v>
       </c>
       <c r="E25" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>954</v>
+        <f ca="1"/>
+        <v>1322.5</v>
       </c>
       <c r="F25" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.13785737758790662</v>
+        <f ca="1"/>
+        <v>0.19516102530397639</v>
       </c>
       <c r="G25" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H25">
         <v>1.63</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>131152</v>
       </c>
@@ -1842,22 +1809,22 @@
         <v>583.0454545454545</v>
       </c>
       <c r="E26" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>284</v>
+        <f ca="1"/>
+        <v>566.5</v>
       </c>
       <c r="F26" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.51290247134949718</v>
+        <f ca="1"/>
+        <v>-2.8377640913697655E-2</v>
       </c>
       <c r="G26" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H26">
         <v>1.63</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>131153</v>
       </c>
@@ -1871,22 +1838,22 @@
         <v>473.86363636363637</v>
       </c>
       <c r="E27" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>243</v>
+        <f ca="1"/>
+        <v>513</v>
       </c>
       <c r="F27" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.4871942446043166</v>
+        <f ca="1"/>
+        <v>8.2589928057553941E-2</v>
       </c>
       <c r="G27" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H27">
         <v>1.63</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>131154</v>
       </c>
@@ -1900,22 +1867,22 @@
         <v>252.63636363636363</v>
       </c>
       <c r="E28" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>339</v>
+        <f ca="1"/>
+        <v>395</v>
       </c>
       <c r="F28" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>0.34184958618207983</v>
+        <f ca="1"/>
+        <v>0.5635120546959338</v>
       </c>
       <c r="G28" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
+        <f ca="1"/>
         <v>SUBIÓ</v>
       </c>
       <c r="H28">
         <v>1.63</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>131155</v>
       </c>
@@ -1929,22 +1896,22 @@
         <v>308.81818181818181</v>
       </c>
       <c r="E29" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>361</v>
+        <f ca="1"/>
+        <v>510</v>
       </c>
       <c r="F29" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>0.16897262290256121</v>
+        <f ca="1"/>
+        <v>0.65145716808949072</v>
       </c>
       <c r="G29" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
+        <f ca="1"/>
         <v>SUBIÓ</v>
       </c>
       <c r="H29">
         <v>1.63</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>131700</v>
       </c>
@@ -1958,22 +1925,22 @@
         <v>137.77272727272728</v>
       </c>
       <c r="E30" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>55</v>
+        <f ca="1"/>
+        <v>77</v>
       </c>
       <c r="F30" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.60079181788188718</v>
+        <f ca="1"/>
+        <v>-0.44110854503464203</v>
       </c>
       <c r="G30" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H30">
         <v>6.15</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>131701</v>
       </c>
@@ -1987,22 +1954,22 @@
         <v>152.22727272727272</v>
       </c>
       <c r="E31" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>80</v>
+        <f ca="1"/>
+        <v>149</v>
       </c>
       <c r="F31" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.47446999104210208</v>
+        <f ca="1"/>
+        <v>-2.1200358315915158E-2</v>
       </c>
       <c r="G31" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H31">
         <v>6.15</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>132150</v>
       </c>
@@ -2016,22 +1983,22 @@
         <v>821.81818181818187</v>
       </c>
       <c r="E32" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>561</v>
+        <f ca="1"/>
+        <v>958</v>
       </c>
       <c r="F32" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.31736725663716814</v>
+        <f ca="1"/>
+        <v>0.16570796460176984</v>
       </c>
       <c r="G32" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>132151</v>
       </c>
@@ -2045,22 +2012,22 @@
         <v>628.86363636363637</v>
       </c>
       <c r="E33" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>339</v>
+        <f ca="1"/>
+        <v>655</v>
       </c>
       <c r="F33" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.46093241778099026</v>
+        <f ca="1"/>
+        <v>4.1561257679797681E-2</v>
       </c>
       <c r="G33" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H33">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>132152</v>
       </c>
@@ -2074,22 +2041,22 @@
         <v>828.4545454545455</v>
       </c>
       <c r="E34" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>498</v>
+        <f ca="1"/>
+        <v>873</v>
       </c>
       <c r="F34" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-0.39888071985076268</v>
+        <f ca="1"/>
+        <v>5.3769340502578755E-2</v>
       </c>
       <c r="G34" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H34">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>132153</v>
       </c>
@@ -2103,22 +2070,22 @@
         <v>553.86363636363637</v>
       </c>
       <c r="E35" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>351</v>
+        <f ca="1"/>
+        <v>585.5</v>
       </c>
       <c r="F35" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.36627000410340582</v>
+        <f ca="1"/>
+        <v>5.7119409109560815E-2</v>
       </c>
       <c r="G35" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H35">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>134000</v>
       </c>
@@ -2132,22 +2099,22 @@
         <v>3.7272727272727271</v>
       </c>
       <c r="E36" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>1</v>
+        <f ca="1"/>
+        <v>3</v>
       </c>
       <c r="F36" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-0.73170731707317072</v>
+        <f ca="1"/>
+        <v>-0.19512195121951215</v>
       </c>
       <c r="G36" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H36">
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>134001</v>
       </c>
@@ -2161,22 +2128,22 @@
         <v>0.5</v>
       </c>
       <c r="E37" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
+        <f ca="1"/>
         <v>0</v>
       </c>
       <c r="F37" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
+        <f ca="1"/>
         <v>-1</v>
       </c>
       <c r="G37" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H37">
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>140230</v>
       </c>
@@ -2190,22 +2157,22 @@
         <v>124.68181818181819</v>
       </c>
       <c r="E38" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>56</v>
+        <f ca="1"/>
+        <v>60</v>
       </c>
       <c r="F38" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.55085672621217641</v>
+        <f ca="1"/>
+        <v>-0.51877506379876048</v>
       </c>
       <c r="G38" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H38">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>140231</v>
       </c>
@@ -2219,22 +2186,22 @@
         <v>602.81818181818187</v>
       </c>
       <c r="E39" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>371</v>
+        <f ca="1"/>
+        <v>618.5</v>
       </c>
       <c r="F39" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-0.38455738199366618</v>
+        <f ca="1"/>
+        <v>2.6014175840747944E-2</v>
       </c>
       <c r="G39" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H39">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>140232</v>
       </c>
@@ -2248,22 +2215,22 @@
         <v>430.86363636363637</v>
       </c>
       <c r="E40" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>342</v>
+        <f ca="1"/>
+        <v>460</v>
       </c>
       <c r="F40" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.20624538453423358</v>
+        <f ca="1"/>
+        <v>6.7623167000738338E-2</v>
       </c>
       <c r="G40" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H40">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>150360</v>
       </c>
@@ -2277,22 +2244,22 @@
         <v>276.18181818181819</v>
       </c>
       <c r="E41" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>202</v>
+        <f ca="1"/>
+        <v>310</v>
       </c>
       <c r="F41" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>-0.26859776168531935</v>
+        <f ca="1"/>
+        <v>0.12244897959183665</v>
       </c>
       <c r="G41" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H41">
         <v>0.81</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>150361</v>
       </c>
@@ -2306,22 +2273,22 @@
         <v>509.31818181818181</v>
       </c>
       <c r="E42" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>330</v>
+        <f ca="1"/>
+        <v>575</v>
       </c>
       <c r="F42" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-0.35207496653279791</v>
+        <f ca="1"/>
+        <v>0.12896028558679151</v>
       </c>
       <c r="G42" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H42">
         <v>0.81</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>150362</v>
       </c>
@@ -2335,22 +2302,22 @@
         <v>318.95454545454544</v>
       </c>
       <c r="E43" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>151</v>
+        <f ca="1"/>
+        <v>292</v>
       </c>
       <c r="F43" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.52657830981901088</v>
+        <f ca="1"/>
+        <v>-8.4509049451332419E-2</v>
       </c>
       <c r="G43" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H43">
         <v>0.81</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>150363</v>
       </c>
@@ -2364,22 +2331,22 @@
         <v>304.04545454545456</v>
       </c>
       <c r="E44" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>216</v>
+        <f ca="1"/>
+        <v>316</v>
       </c>
       <c r="F44" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.28957990731050987</v>
+        <f ca="1"/>
+        <v>3.9318283749439242E-2</v>
       </c>
       <c r="G44" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
-        <v>BAJO</v>
+        <f ca="1"/>
+        <v>SUBIÓ</v>
       </c>
       <c r="H44">
         <v>0.81</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>151500</v>
       </c>
@@ -2393,22 +2360,22 @@
         <v>60.31818181818182</v>
       </c>
       <c r="E45" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>16</v>
+        <f ca="1"/>
+        <v>31.5</v>
       </c>
       <c r="F45" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.73474001507159004</v>
+        <f ca="1"/>
+        <v>-0.47776940467219298</v>
       </c>
       <c r="G45" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H45">
         <v>2.62</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>151501</v>
       </c>
@@ -2422,22 +2389,22 @@
         <v>117.72727272727273</v>
       </c>
       <c r="E46" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>24</v>
+        <f ca="1"/>
+        <v>65</v>
       </c>
       <c r="F46" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>-0.79613899613899619</v>
+        <f ca="1"/>
+        <v>-0.44787644787644787</v>
       </c>
       <c r="G46" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H46">
         <v>2.62</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>151502</v>
       </c>
@@ -2451,22 +2418,22 @@
         <v>41.363636363636367</v>
       </c>
       <c r="E47" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>12</v>
+        <f ca="1"/>
+        <v>25.5</v>
       </c>
       <c r="F47" s="5">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>-0.70989010989010992</v>
+        <f ca="1"/>
+        <v>-0.3835164835164836</v>
       </c>
       <c r="G47" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H47">
         <v>2.62</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>151503</v>
       </c>
@@ -2480,15 +2447,15 @@
         <v>50.090909090909093</v>
       </c>
       <c r="E48" s="4">
-        <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>16</v>
+        <f ca="1"/>
+        <v>34</v>
       </c>
       <c r="F48" s="6">
-        <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>-0.68058076225045372</v>
+        <f ca="1"/>
+        <v>-0.32123411978221417</v>
       </c>
       <c r="G48" s="7" t="str">
-        <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>
+        <f ca="1"/>
         <v>BAJO</v>
       </c>
       <c r="H48">
@@ -2506,9 +2473,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -2516,7 +2483,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>

--- a/data/Comparación de Venta Diaria por SKU.xlsx
+++ b/data/Comparación de Venta Diaria por SKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{0E5779F7-8682-44DE-88C6-83F206C2BBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D94364-479A-45E7-A3EB-F1618C20256A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -411,455 +411,554 @@
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
-    <oleItems>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x14">
-          <x14:oleItem name="!DESV. VTS BY SKU!F4C6:F50C6" advise="1">
-            <x14:values rows="47">
-              <value>
-                <val>1379.5</val>
-              </value>
-              <value>
-                <val>1.5</val>
-              </value>
-              <value>
-                <val>622</val>
-              </value>
-              <value>
-                <val>86.5</val>
-              </value>
-              <value>
-                <val>8.5</val>
-              </value>
-              <value>
-                <val>2007</val>
-              </value>
-              <value>
-                <val>211</val>
-              </value>
-              <value>
-                <val>445.5</val>
-              </value>
-              <value>
-                <val>824.5</val>
-              </value>
-              <value>
-                <val>334</val>
-              </value>
-              <value>
-                <val>3894.5</val>
-              </value>
-              <value>
-                <val>2513.5</val>
-              </value>
-              <value>
-                <val>2404</val>
-              </value>
-              <value>
-                <val>2877</val>
-              </value>
-              <value>
-                <val>775</val>
-              </value>
-              <value>
-                <val>1050</val>
-              </value>
-              <value>
-                <val>1029</val>
-              </value>
-              <value>
-                <val>208</val>
-              </value>
-              <value>
-                <val>99</val>
-              </value>
-              <value>
-                <val>461</val>
-              </value>
-              <value>
-                <val>796</val>
-              </value>
-              <value>
-                <val>130</val>
-              </value>
-              <value>
-                <val>777</val>
-              </value>
-              <value>
-                <val>1322.5</val>
-              </value>
-              <value>
-                <val>566.5</val>
-              </value>
-              <value>
-                <val>513</val>
-              </value>
-              <value>
-                <val>395</val>
-              </value>
-              <value>
-                <val>510</val>
-              </value>
-              <value>
-                <val>77</val>
-              </value>
-              <value>
-                <val>149</val>
-              </value>
-              <value>
-                <val>958</val>
-              </value>
-              <value>
-                <val>655</val>
-              </value>
-              <value>
-                <val>873</val>
-              </value>
-              <value>
-                <val>585.5</val>
-              </value>
-              <value>
-                <val>3</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>60</val>
-              </value>
-              <value>
-                <val>618.5</val>
-              </value>
-              <value>
-                <val>460</val>
-              </value>
-              <value>
-                <val>310</val>
-              </value>
-              <value>
-                <val>575</val>
-              </value>
-              <value>
-                <val>292</val>
-              </value>
-              <value>
-                <val>316</val>
-              </value>
-              <value>
-                <val>31.5</val>
-              </value>
-              <value>
-                <val>65</val>
-              </value>
-              <value>
-                <val>25.5</val>
-              </value>
-              <value>
-                <val>34</val>
-              </value>
-            </x14:values>
-          </x14:oleItem>
-        </mc:Choice>
-        <mc:Fallback>
-          <oleItem name="!DESV. VTS BY SKU!F4C6:F50C6" advise="1"/>
-        </mc:Fallback>
-      </mc:AlternateContent>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x14">
-          <x14:oleItem name="!DESV. VTS BY SKU!F4C7:F50C8" advise="1">
-            <x14:values rows="47" cols="2">
-              <value>
-                <val>0.13961173068979771</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>-0.96529968454258674</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>0.25645028004774573</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>-0.21622734761120266</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>-0.43674698795180722</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>0.4188303341902313</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>0.39441273655752473</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>0.3372902169463774</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>1.1712867421495909E-2</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>-0.16764839148164923</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>0.13168843862684754</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>0.16240987156040432</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>0.10688348925305036</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>7.7729911968533516E-2</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>6.1511642385755128E-2</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>0.20012468827930174</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>0.18164735358596928</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>-0.26678416920365322</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>-0.30879086004443035</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>-0.12213277936466715</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>-0.11237264939936131</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>0.98611111111111116</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>8.4438241451500362E-2</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>0.19516102530397639</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>-2.8377640913697655E-2</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>8.2589928057553941E-2</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>0.5635120546959338</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>0.65145716808949072</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>-0.44110854503464203</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>-2.1200358315915158E-2</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>0.16570796460176984</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>4.1561257679797681E-2</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>5.3769340502578755E-2</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>5.7119409109560815E-2</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>-0.19512195121951215</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>-1</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>-0.51877506379876048</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>2.6014175840747944E-2</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>6.7623167000738338E-2</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>0.12244897959183665</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>0.12896028558679151</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>-8.4509049451332419E-2</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>3.9318283749439242E-2</val>
-              </value>
-              <value t="str">
-                <val>SUBIÓ</val>
-              </value>
-              <value>
-                <val>-0.47776940467219298</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>-0.44787644787644787</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>-0.3835164835164836</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-              <value>
-                <val>-0.32123411978221417</val>
-              </value>
-              <value t="str">
-                <val>BAJO</val>
-              </value>
-            </x14:values>
-          </x14:oleItem>
-        </mc:Choice>
-        <mc:Fallback>
-          <oleItem name="!DESV. VTS BY SKU!F4C7:F50C8" advise="1"/>
-        </mc:Fallback>
-      </mc:AlternateContent>
-    </oleItems>
-  </oleLink>
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="INVENTARIO NACIONAL 01-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 02-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 05-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 06-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 07-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 08-10-2 "/>
+      <sheetName val="CCC"/>
+      <sheetName val="VINCULO VTS BY SKU SEPTIEMBRE"/>
+      <sheetName val="VINCULO VTS BY SKU OPEN"/>
+      <sheetName val="DESV. VTS BY SKU"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
+        <row r="4">
+          <cell r="F4">
+            <v>1170.5</v>
+          </cell>
+          <cell r="G4">
+            <v>-3.3044196612969867E-2</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5">
+            <v>8.3333333333333339</v>
+          </cell>
+          <cell r="G5">
+            <v>-0.80722046968103744</v>
+          </cell>
+          <cell r="H5" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6">
+            <v>491</v>
+          </cell>
+          <cell r="G6">
+            <v>-8.1718850426958367E-3</v>
+          </cell>
+          <cell r="H6" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="F7">
+            <v>88.5</v>
+          </cell>
+          <cell r="G7">
+            <v>-0.19810543657331137</v>
+          </cell>
+          <cell r="H7" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="F8">
+            <v>11.166666666666666</v>
+          </cell>
+          <cell r="G8">
+            <v>-0.26004016064257041</v>
+          </cell>
+          <cell r="H8" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="F9">
+            <v>1524</v>
+          </cell>
+          <cell r="G9">
+            <v>7.7377892030848328E-2</v>
+          </cell>
+          <cell r="H9" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="F10">
+            <v>159.66666666666666</v>
+          </cell>
+          <cell r="G10">
+            <v>5.5171723240212245E-2</v>
+          </cell>
+          <cell r="H10" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="F11">
+            <v>408.83333333333331</v>
+          </cell>
+          <cell r="G11">
+            <v>0.22722517851457669</v>
+          </cell>
+          <cell r="H11" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="F12">
+            <v>823.16666666666663</v>
+          </cell>
+          <cell r="G12">
+            <v>1.0076784353096446E-2</v>
+          </cell>
+          <cell r="H12" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="F13">
+            <v>369.5</v>
+          </cell>
+          <cell r="G13">
+            <v>-7.9179882193022189E-2</v>
+          </cell>
+          <cell r="H13" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="F14">
+            <v>3576.5</v>
+          </cell>
+          <cell r="G14">
+            <v>3.928198761045576E-2</v>
+          </cell>
+          <cell r="H14" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="F15">
+            <v>2157.1666666666665</v>
+          </cell>
+          <cell r="G15">
+            <v>-2.3824038454802743E-3</v>
+          </cell>
+          <cell r="H15" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="F16">
+            <v>2114.6666666666665</v>
+          </cell>
+          <cell r="G16">
+            <v>-2.6335433191715052E-2</v>
+          </cell>
+          <cell r="H16" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="F17">
+            <v>2682.8333333333335</v>
+          </cell>
+          <cell r="G17">
+            <v>4.9946931385402848E-3</v>
+          </cell>
+          <cell r="H17" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="F18">
+            <v>796</v>
+          </cell>
+          <cell r="G18">
+            <v>9.027518366330467E-2</v>
+          </cell>
+          <cell r="H18" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="F19">
+            <v>1054.1666666666667</v>
+          </cell>
+          <cell r="G19">
+            <v>0.20488708783596588</v>
+          </cell>
+          <cell r="H19" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="F20">
+            <v>1017.6666666666666</v>
+          </cell>
+          <cell r="G20">
+            <v>0.16863277308000124</v>
+          </cell>
+          <cell r="H20" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="F21">
+            <v>279</v>
+          </cell>
+          <cell r="G21">
+            <v>-1.6503765422207994E-2</v>
+          </cell>
+          <cell r="H21" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="F22">
+            <v>135.66666666666666</v>
+          </cell>
+          <cell r="G22">
+            <v>-5.2787474875700902E-2</v>
+          </cell>
+          <cell r="H22" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="F23">
+            <v>510.16666666666669</v>
+          </cell>
+          <cell r="G23">
+            <v>-2.850630427883083E-2</v>
+          </cell>
+          <cell r="H23" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="F24">
+            <v>861.66666666666663</v>
+          </cell>
+          <cell r="G24">
+            <v>-3.9147110007265118E-2</v>
+          </cell>
+          <cell r="H24" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="F25">
+            <v>43.333333333333336</v>
+          </cell>
+          <cell r="G25">
+            <v>-0.33796296296296291</v>
+          </cell>
+          <cell r="H25" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="F26">
+            <v>623.5</v>
+          </cell>
+          <cell r="G26">
+            <v>-0.12979762735519884</v>
+          </cell>
+          <cell r="H26" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="F27">
+            <v>1032.5</v>
+          </cell>
+          <cell r="G27">
+            <v>-6.6915872494249018E-2</v>
+          </cell>
+          <cell r="H27" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="F28">
+            <v>594.33333333333337</v>
+          </cell>
+          <cell r="G28">
+            <v>1.9360203736909165E-2</v>
+          </cell>
+          <cell r="H28" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="F29">
+            <v>490.66666666666669</v>
+          </cell>
+          <cell r="G29">
+            <v>3.5459632294164711E-2</v>
+          </cell>
+          <cell r="H29" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="F30">
+            <v>276.83333333333331</v>
+          </cell>
+          <cell r="G30">
+            <v>9.5777857742593175E-2</v>
+          </cell>
+          <cell r="H30" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="F31">
+            <v>299.33333333333331</v>
+          </cell>
+          <cell r="G31">
+            <v>-3.0713374546168182E-2</v>
+          </cell>
+          <cell r="H31" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="F32">
+            <v>103.66666666666667</v>
+          </cell>
+          <cell r="G32">
+            <v>-0.247553062795557</v>
+          </cell>
+          <cell r="H32" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="F33">
+            <v>124.83333333333333</v>
+          </cell>
+          <cell r="G33">
+            <v>-0.17995421518861354</v>
+          </cell>
+          <cell r="H33" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="F34">
+            <v>845.16666666666663</v>
+          </cell>
+          <cell r="G34">
+            <v>2.841076696165179E-2</v>
+          </cell>
+          <cell r="H34" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="F35">
+            <v>598.66666666666663</v>
+          </cell>
+          <cell r="G35">
+            <v>-4.8018311046861939E-2</v>
+          </cell>
+          <cell r="H35" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="F36">
+            <v>786.33333333333337</v>
+          </cell>
+          <cell r="G36">
+            <v>-5.0843117890193468E-2</v>
+          </cell>
+          <cell r="H36" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="F37">
+            <v>516.16666666666663</v>
+          </cell>
+          <cell r="G37">
+            <v>-6.8061824647791092E-2</v>
+          </cell>
+          <cell r="H37" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="F38">
+            <v>3.5</v>
+          </cell>
+          <cell r="G38">
+            <v>-6.0975609756097504E-2</v>
+          </cell>
+          <cell r="H38" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="F39">
+            <v>1.3333333333333333</v>
+          </cell>
+          <cell r="G39">
+            <v>1.6666666666666665</v>
+          </cell>
+          <cell r="H39" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="F40">
+            <v>37.333333333333336</v>
+          </cell>
+          <cell r="G40">
+            <v>-0.7005711508081176</v>
+          </cell>
+          <cell r="H40" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="F41">
+            <v>608.33333333333337</v>
+          </cell>
+          <cell r="G41">
+            <v>9.1489468657315332E-3</v>
+          </cell>
+          <cell r="H41" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="F42">
+            <v>440.83333333333331</v>
+          </cell>
+          <cell r="G42">
+            <v>2.3138868375707666E-2</v>
+          </cell>
+          <cell r="H42" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="F43">
+            <v>276.5</v>
+          </cell>
+          <cell r="G43">
+            <v>1.1520737327188613E-3</v>
+          </cell>
+          <cell r="H43" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="F44">
+            <v>483.33333333333331</v>
+          </cell>
+          <cell r="G44">
+            <v>-5.1018890376320125E-2</v>
+          </cell>
+          <cell r="H44" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="F45">
+            <v>258.66666666666669</v>
+          </cell>
+          <cell r="G45">
+            <v>-0.1890171488290342</v>
+          </cell>
+          <cell r="H45" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="F46">
+            <v>270</v>
+          </cell>
+          <cell r="G46">
+            <v>-0.11197488413813728</v>
+          </cell>
+          <cell r="H46" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="F47">
+            <v>40.333333333333336</v>
+          </cell>
+          <cell r="G47">
+            <v>-0.33132378799296658</v>
+          </cell>
+          <cell r="H47" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="F48">
+            <v>84.5</v>
+          </cell>
+          <cell r="G48">
+            <v>-0.28223938223938227</v>
+          </cell>
+          <cell r="H48" t="str">
+            <v>BAJO</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="F49">
+            <v>51.833333333333336</v>
+          </cell>
+          <cell r="G49">
+            <v>0.2531135531135531</v>
+          </cell>
+          <cell r="H49" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="F50">
+            <v>53.833333333333336</v>
+          </cell>
+          <cell r="G50">
+            <v>7.4712643678160884E-2</v>
+          </cell>
+          <cell r="H50" t="str">
+            <v>SUBIÓ</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
 </externalLink>
 </file>
 
@@ -1062,18 +1161,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" customWidth="1"/>
-    <col min="6" max="8" width="17.6640625" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="8" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1099,7 +1198,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>110150</v>
       </c>
@@ -1113,22 +1212,22 @@
         <v>1210.5</v>
       </c>
       <c r="E2" s="4">
-        <f t="array" aca="1" ref="E2:E48" ca="1">[1]!'!DESV. VTS BY SKU!F4C6:F50C6'</f>
-        <v>1379.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
+        <v>1170.5</v>
       </c>
       <c r="F2" s="5">
-        <f t="array" aca="1" ref="F2:G48" ca="1">[1]!'!DESV. VTS BY SKU!F4C7:F50C8'</f>
-        <v>0.13961173068979771</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
+        <v>-3.3044196612969867E-2</v>
       </c>
       <c r="G2" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
+        <v>BAJO</v>
       </c>
       <c r="H2">
         <v>1.36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>110151</v>
       </c>
@@ -1142,22 +1241,22 @@
         <v>43.227272727272727</v>
       </c>
       <c r="E3" s="4">
-        <f ca="1"/>
-        <v>1.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
+        <v>8.3333333333333339</v>
       </c>
       <c r="F3" s="6">
-        <f ca="1"/>
-        <v>-0.96529968454258674</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
+        <v>-0.80722046968103744</v>
       </c>
       <c r="G3" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
         <v>BAJO</v>
       </c>
       <c r="H3">
         <v>1.59</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>110230</v>
       </c>
@@ -1171,22 +1270,22 @@
         <v>495.04545454545456</v>
       </c>
       <c r="E4" s="4">
-        <f ca="1"/>
-        <v>622</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
+        <v>491</v>
       </c>
       <c r="F4" s="5">
-        <f ca="1"/>
-        <v>0.25645028004774573</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
+        <v>-8.1718850426958367E-3</v>
       </c>
       <c r="G4" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
+        <v>BAJO</v>
       </c>
       <c r="H4">
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>110400</v>
       </c>
@@ -1200,22 +1299,22 @@
         <v>110.36363636363636</v>
       </c>
       <c r="E5" s="4">
-        <f ca="1"/>
-        <v>86.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
+        <v>88.5</v>
       </c>
       <c r="F5" s="6">
-        <f ca="1"/>
-        <v>-0.21622734761120266</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
+        <v>-0.19810543657331137</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
         <v>BAJO</v>
       </c>
       <c r="H5">
         <v>3.61</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>111000</v>
       </c>
@@ -1229,22 +1328,22 @@
         <v>15.090909090909092</v>
       </c>
       <c r="E6" s="4">
-        <f ca="1"/>
-        <v>8.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
+        <v>11.166666666666666</v>
       </c>
       <c r="F6" s="5">
-        <f ca="1"/>
-        <v>-0.43674698795180722</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
+        <v>-0.26004016064257041</v>
       </c>
       <c r="G6" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
         <v>BAJO</v>
       </c>
       <c r="H6">
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>120130</v>
       </c>
@@ -1258,22 +1357,22 @@
         <v>1414.5454545454545</v>
       </c>
       <c r="E7" s="4">
-        <f ca="1"/>
-        <v>2007</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
+        <v>1524</v>
       </c>
       <c r="F7" s="6">
-        <f ca="1"/>
-        <v>0.4188303341902313</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
+        <v>7.7377892030848328E-2</v>
       </c>
       <c r="G7" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H7">
         <v>0.63</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>120131</v>
       </c>
@@ -1287,22 +1386,22 @@
         <v>151.31818181818181</v>
       </c>
       <c r="E8" s="4">
-        <f ca="1"/>
-        <v>211</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
+        <v>159.66666666666666</v>
       </c>
       <c r="F8" s="5">
-        <f ca="1"/>
-        <v>0.39441273655752473</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
+        <v>5.5171723240212245E-2</v>
       </c>
       <c r="G8" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H8">
         <v>0.63</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>120132</v>
       </c>
@@ -1316,22 +1415,22 @@
         <v>333.13636363636363</v>
       </c>
       <c r="E9" s="4">
-        <f ca="1"/>
-        <v>445.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
+        <v>408.83333333333331</v>
       </c>
       <c r="F9" s="6">
-        <f ca="1"/>
-        <v>0.3372902169463774</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
+        <v>0.22722517851457669</v>
       </c>
       <c r="G9" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H9">
         <v>0.63</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>130150</v>
       </c>
@@ -1345,22 +1444,22 @@
         <v>814.9545454545455</v>
       </c>
       <c r="E10" s="4">
-        <f ca="1"/>
-        <v>824.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
+        <v>823.16666666666663</v>
       </c>
       <c r="F10" s="5">
-        <f ca="1"/>
-        <v>1.1712867421495909E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
+        <v>1.0076784353096446E-2</v>
       </c>
       <c r="G10" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H10">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>130151</v>
       </c>
@@ -1374,22 +1473,22 @@
         <v>401.27272727272725</v>
       </c>
       <c r="E11" s="4">
-        <f ca="1"/>
-        <v>334</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
+        <v>369.5</v>
       </c>
       <c r="F11" s="6">
-        <f ca="1"/>
-        <v>-0.16764839148164923</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
+        <v>-7.9179882193022189E-2</v>
       </c>
       <c r="G11" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
         <v>BAJO</v>
       </c>
       <c r="H11">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>130152</v>
       </c>
@@ -1403,22 +1502,22 @@
         <v>3441.318181818182</v>
       </c>
       <c r="E12" s="4">
-        <f ca="1"/>
-        <v>3894.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
+        <v>3576.5</v>
       </c>
       <c r="F12" s="5">
-        <f ca="1"/>
-        <v>0.13168843862684754</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
+        <v>3.928198761045576E-2</v>
       </c>
       <c r="G12" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H12">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>130153</v>
       </c>
@@ -1432,22 +1531,22 @@
         <v>2162.318181818182</v>
       </c>
       <c r="E13" s="4">
-        <f ca="1"/>
-        <v>2513.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
+        <v>2157.1666666666665</v>
       </c>
       <c r="F13" s="6">
-        <f ca="1"/>
-        <v>0.16240987156040432</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
+        <v>-2.3824038454802743E-3</v>
       </c>
       <c r="G13" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
+        <v>BAJO</v>
       </c>
       <c r="H13">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>130154</v>
       </c>
@@ -1461,22 +1560,22 @@
         <v>2171.8636363636365</v>
       </c>
       <c r="E14" s="4">
-        <f ca="1"/>
-        <v>2404</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
+        <v>2114.6666666666665</v>
       </c>
       <c r="F14" s="5">
-        <f ca="1"/>
-        <v>0.10688348925305036</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
+        <v>-2.6335433191715052E-2</v>
       </c>
       <c r="G14" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
+        <v>BAJO</v>
       </c>
       <c r="H14">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>130155</v>
       </c>
@@ -1490,22 +1589,22 @@
         <v>2669.5</v>
       </c>
       <c r="E15" s="4">
-        <f ca="1"/>
-        <v>2877</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
+        <v>2682.8333333333335</v>
       </c>
       <c r="F15" s="6">
-        <f ca="1"/>
-        <v>7.7729911968533516E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
+        <v>4.9946931385402848E-3</v>
       </c>
       <c r="G15" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H15">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>130157</v>
       </c>
@@ -1519,22 +1618,22 @@
         <v>730.09090909090912</v>
       </c>
       <c r="E16" s="4">
-        <f ca="1"/>
-        <v>775</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
+        <v>796</v>
       </c>
       <c r="F16" s="6">
-        <f ca="1"/>
-        <v>6.1511642385755128E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
+        <v>9.027518366330467E-2</v>
       </c>
       <c r="G16" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H16">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>130158</v>
       </c>
@@ -1548,22 +1647,22 @@
         <v>874.90909090909088</v>
       </c>
       <c r="E17" s="4">
-        <f ca="1"/>
-        <v>1050</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
+        <v>1054.1666666666667</v>
       </c>
       <c r="F17" s="6">
-        <f ca="1"/>
-        <v>0.20012468827930174</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
+        <v>0.20488708783596588</v>
       </c>
       <c r="G17" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H17">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>130159</v>
       </c>
@@ -1577,22 +1676,22 @@
         <v>870.81818181818187</v>
       </c>
       <c r="E18" s="4">
-        <f ca="1"/>
-        <v>1029</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
+        <v>1017.6666666666666</v>
       </c>
       <c r="F18" s="6">
-        <f ca="1"/>
-        <v>0.18164735358596928</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
+        <v>0.16863277308000124</v>
       </c>
       <c r="G18" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H18">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>130700</v>
       </c>
@@ -1606,22 +1705,22 @@
         <v>283.68181818181819</v>
       </c>
       <c r="E19" s="4">
-        <f ca="1"/>
-        <v>208</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
+        <v>279</v>
       </c>
       <c r="F19" s="6">
-        <f ca="1"/>
-        <v>-0.26678416920365322</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
+        <v>-1.6503765422207994E-2</v>
       </c>
       <c r="G19" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
         <v>BAJO</v>
       </c>
       <c r="H19">
         <v>3.68</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>130701</v>
       </c>
@@ -1635,22 +1734,22 @@
         <v>143.22727272727272</v>
       </c>
       <c r="E20" s="4">
-        <f ca="1"/>
-        <v>99</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
+        <v>135.66666666666666</v>
       </c>
       <c r="F20" s="5">
-        <f ca="1"/>
-        <v>-0.30879086004443035</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
+        <v>-5.2787474875700902E-2</v>
       </c>
       <c r="G20" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
         <v>BAJO</v>
       </c>
       <c r="H20">
         <v>3.68</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>130702</v>
       </c>
@@ -1664,22 +1763,22 @@
         <v>525.13636363636363</v>
       </c>
       <c r="E21" s="4">
-        <f ca="1"/>
-        <v>461</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
+        <v>510.16666666666669</v>
       </c>
       <c r="F21" s="6">
-        <f ca="1"/>
-        <v>-0.12213277936466715</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
+        <v>-2.850630427883083E-2</v>
       </c>
       <c r="G21" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
         <v>BAJO</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>130703</v>
       </c>
@@ -1693,22 +1792,22 @@
         <v>896.77272727272725</v>
       </c>
       <c r="E22" s="4">
-        <f ca="1"/>
-        <v>796</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
+        <v>861.66666666666663</v>
       </c>
       <c r="F22" s="5">
-        <f ca="1"/>
-        <v>-0.11237264939936131</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
+        <v>-3.9147110007265118E-2</v>
       </c>
       <c r="G22" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
         <v>BAJO</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>130707</v>
       </c>
@@ -1722,22 +1821,22 @@
         <v>65.454545454545453</v>
       </c>
       <c r="E23" s="4">
-        <f ca="1"/>
-        <v>130</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
+        <v>43.333333333333336</v>
       </c>
       <c r="F23" s="5">
-        <f ca="1"/>
-        <v>0.98611111111111116</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
+        <v>-0.33796296296296291</v>
       </c>
       <c r="G23" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
+        <v>BAJO</v>
       </c>
       <c r="H23">
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>131150</v>
       </c>
@@ -1751,22 +1850,22 @@
         <v>716.5</v>
       </c>
       <c r="E24" s="4">
-        <f ca="1"/>
-        <v>777</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
+        <v>623.5</v>
       </c>
       <c r="F24" s="6">
-        <f ca="1"/>
-        <v>8.4438241451500362E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
+        <v>-0.12979762735519884</v>
       </c>
       <c r="G24" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
+        <v>BAJO</v>
       </c>
       <c r="H24">
         <v>1.63</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>131151</v>
       </c>
@@ -1780,22 +1879,22 @@
         <v>1106.5454545454545</v>
       </c>
       <c r="E25" s="4">
-        <f ca="1"/>
-        <v>1322.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
+        <v>1032.5</v>
       </c>
       <c r="F25" s="5">
-        <f ca="1"/>
-        <v>0.19516102530397639</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
+        <v>-6.6915872494249018E-2</v>
       </c>
       <c r="G25" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
+        <v>BAJO</v>
       </c>
       <c r="H25">
         <v>1.63</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>131152</v>
       </c>
@@ -1809,22 +1908,22 @@
         <v>583.0454545454545</v>
       </c>
       <c r="E26" s="4">
-        <f ca="1"/>
-        <v>566.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
+        <v>594.33333333333337</v>
       </c>
       <c r="F26" s="6">
-        <f ca="1"/>
-        <v>-2.8377640913697655E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
+        <v>1.9360203736909165E-2</v>
       </c>
       <c r="G26" s="7" t="str">
-        <f ca="1"/>
-        <v>BAJO</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H26">
         <v>1.63</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>131153</v>
       </c>
@@ -1838,22 +1937,22 @@
         <v>473.86363636363637</v>
       </c>
       <c r="E27" s="4">
-        <f ca="1"/>
-        <v>513</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
+        <v>490.66666666666669</v>
       </c>
       <c r="F27" s="5">
-        <f ca="1"/>
-        <v>8.2589928057553941E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
+        <v>3.5459632294164711E-2</v>
       </c>
       <c r="G27" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H27">
         <v>1.63</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>131154</v>
       </c>
@@ -1867,22 +1966,22 @@
         <v>252.63636363636363</v>
       </c>
       <c r="E28" s="4">
-        <f ca="1"/>
-        <v>395</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
+        <v>276.83333333333331</v>
       </c>
       <c r="F28" s="5">
-        <f ca="1"/>
-        <v>0.5635120546959338</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
+        <v>9.5777857742593175E-2</v>
       </c>
       <c r="G28" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H28">
         <v>1.63</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>131155</v>
       </c>
@@ -1896,22 +1995,22 @@
         <v>308.81818181818181</v>
       </c>
       <c r="E29" s="4">
-        <f ca="1"/>
-        <v>510</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
+        <v>299.33333333333331</v>
       </c>
       <c r="F29" s="5">
-        <f ca="1"/>
-        <v>0.65145716808949072</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
+        <v>-3.0713374546168182E-2</v>
       </c>
       <c r="G29" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
+        <v>BAJO</v>
       </c>
       <c r="H29">
         <v>1.63</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>131700</v>
       </c>
@@ -1925,22 +2024,22 @@
         <v>137.77272727272728</v>
       </c>
       <c r="E30" s="4">
-        <f ca="1"/>
-        <v>77</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
+        <v>103.66666666666667</v>
       </c>
       <c r="F30" s="6">
-        <f ca="1"/>
-        <v>-0.44110854503464203</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
+        <v>-0.247553062795557</v>
       </c>
       <c r="G30" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
         <v>BAJO</v>
       </c>
       <c r="H30">
         <v>6.15</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>131701</v>
       </c>
@@ -1954,22 +2053,22 @@
         <v>152.22727272727272</v>
       </c>
       <c r="E31" s="4">
-        <f ca="1"/>
-        <v>149</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
+        <v>124.83333333333333</v>
       </c>
       <c r="F31" s="5">
-        <f ca="1"/>
-        <v>-2.1200358315915158E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
+        <v>-0.17995421518861354</v>
       </c>
       <c r="G31" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
         <v>BAJO</v>
       </c>
       <c r="H31">
         <v>6.15</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>132150</v>
       </c>
@@ -1983,22 +2082,22 @@
         <v>821.81818181818187</v>
       </c>
       <c r="E32" s="4">
-        <f ca="1"/>
-        <v>958</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
+        <v>845.16666666666663</v>
       </c>
       <c r="F32" s="6">
-        <f ca="1"/>
-        <v>0.16570796460176984</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
+        <v>2.841076696165179E-2</v>
       </c>
       <c r="G32" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H32">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>132151</v>
       </c>
@@ -2012,22 +2111,22 @@
         <v>628.86363636363637</v>
       </c>
       <c r="E33" s="4">
-        <f ca="1"/>
-        <v>655</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
+        <v>598.66666666666663</v>
       </c>
       <c r="F33" s="5">
-        <f ca="1"/>
-        <v>4.1561257679797681E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
+        <v>-4.8018311046861939E-2</v>
       </c>
       <c r="G33" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
+        <v>BAJO</v>
       </c>
       <c r="H33">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>132152</v>
       </c>
@@ -2041,22 +2140,22 @@
         <v>828.4545454545455</v>
       </c>
       <c r="E34" s="4">
-        <f ca="1"/>
-        <v>873</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
+        <v>786.33333333333337</v>
       </c>
       <c r="F34" s="6">
-        <f ca="1"/>
-        <v>5.3769340502578755E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
+        <v>-5.0843117890193468E-2</v>
       </c>
       <c r="G34" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
+        <v>BAJO</v>
       </c>
       <c r="H34">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>132153</v>
       </c>
@@ -2070,22 +2169,22 @@
         <v>553.86363636363637</v>
       </c>
       <c r="E35" s="4">
-        <f ca="1"/>
-        <v>585.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
+        <v>516.16666666666663</v>
       </c>
       <c r="F35" s="5">
-        <f ca="1"/>
-        <v>5.7119409109560815E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
+        <v>-6.8061824647791092E-2</v>
       </c>
       <c r="G35" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
+        <v>BAJO</v>
       </c>
       <c r="H35">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>134000</v>
       </c>
@@ -2099,22 +2198,22 @@
         <v>3.7272727272727271</v>
       </c>
       <c r="E36" s="4">
-        <f ca="1"/>
-        <v>3</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
+        <v>3.5</v>
       </c>
       <c r="F36" s="6">
-        <f ca="1"/>
-        <v>-0.19512195121951215</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
+        <v>-6.0975609756097504E-2</v>
       </c>
       <c r="G36" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
         <v>BAJO</v>
       </c>
       <c r="H36">
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>134001</v>
       </c>
@@ -2128,22 +2227,22 @@
         <v>0.5</v>
       </c>
       <c r="E37" s="4">
-        <f ca="1"/>
-        <v>0</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
+        <v>1.3333333333333333</v>
       </c>
       <c r="F37" s="5">
-        <f ca="1"/>
-        <v>-1</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
+        <v>1.6666666666666665</v>
       </c>
       <c r="G37" s="7" t="str">
-        <f ca="1"/>
-        <v>BAJO</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H37">
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>140230</v>
       </c>
@@ -2157,22 +2256,22 @@
         <v>124.68181818181819</v>
       </c>
       <c r="E38" s="4">
-        <f ca="1"/>
-        <v>60</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
+        <v>37.333333333333336</v>
       </c>
       <c r="F38" s="6">
-        <f ca="1"/>
-        <v>-0.51877506379876048</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
+        <v>-0.7005711508081176</v>
       </c>
       <c r="G38" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
         <v>BAJO</v>
       </c>
       <c r="H38">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>140231</v>
       </c>
@@ -2186,22 +2285,22 @@
         <v>602.81818181818187</v>
       </c>
       <c r="E39" s="4">
-        <f ca="1"/>
-        <v>618.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
+        <v>608.33333333333337</v>
       </c>
       <c r="F39" s="5">
-        <f ca="1"/>
-        <v>2.6014175840747944E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
+        <v>9.1489468657315332E-3</v>
       </c>
       <c r="G39" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H39">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>140232</v>
       </c>
@@ -2215,22 +2314,22 @@
         <v>430.86363636363637</v>
       </c>
       <c r="E40" s="4">
-        <f ca="1"/>
-        <v>460</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
+        <v>440.83333333333331</v>
       </c>
       <c r="F40" s="6">
-        <f ca="1"/>
-        <v>6.7623167000738338E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
+        <v>2.3138868375707666E-2</v>
       </c>
       <c r="G40" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H40">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>150360</v>
       </c>
@@ -2244,22 +2343,22 @@
         <v>276.18181818181819</v>
       </c>
       <c r="E41" s="4">
-        <f ca="1"/>
-        <v>310</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
+        <v>276.5</v>
       </c>
       <c r="F41" s="5">
-        <f ca="1"/>
-        <v>0.12244897959183665</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
+        <v>1.1520737327188613E-3</v>
       </c>
       <c r="G41" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
         <v>SUBIÓ</v>
       </c>
       <c r="H41">
         <v>0.81</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>150361</v>
       </c>
@@ -2273,22 +2372,22 @@
         <v>509.31818181818181</v>
       </c>
       <c r="E42" s="4">
-        <f ca="1"/>
-        <v>575</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
+        <v>483.33333333333331</v>
       </c>
       <c r="F42" s="6">
-        <f ca="1"/>
-        <v>0.12896028558679151</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
+        <v>-5.1018890376320125E-2</v>
       </c>
       <c r="G42" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
+        <v>BAJO</v>
       </c>
       <c r="H42">
         <v>0.81</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>150362</v>
       </c>
@@ -2302,22 +2401,22 @@
         <v>318.95454545454544</v>
       </c>
       <c r="E43" s="4">
-        <f ca="1"/>
-        <v>292</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
+        <v>258.66666666666669</v>
       </c>
       <c r="F43" s="5">
-        <f ca="1"/>
-        <v>-8.4509049451332419E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
+        <v>-0.1890171488290342</v>
       </c>
       <c r="G43" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
         <v>BAJO</v>
       </c>
       <c r="H43">
         <v>0.81</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>150363</v>
       </c>
@@ -2331,22 +2430,22 @@
         <v>304.04545454545456</v>
       </c>
       <c r="E44" s="4">
-        <f ca="1"/>
-        <v>316</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
+        <v>270</v>
       </c>
       <c r="F44" s="6">
-        <f ca="1"/>
-        <v>3.9318283749439242E-2</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
+        <v>-0.11197488413813728</v>
       </c>
       <c r="G44" s="7" t="str">
-        <f ca="1"/>
-        <v>SUBIÓ</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
+        <v>BAJO</v>
       </c>
       <c r="H44">
         <v>0.81</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>151500</v>
       </c>
@@ -2360,22 +2459,22 @@
         <v>60.31818181818182</v>
       </c>
       <c r="E45" s="4">
-        <f ca="1"/>
-        <v>31.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
+        <v>40.333333333333336</v>
       </c>
       <c r="F45" s="5">
-        <f ca="1"/>
-        <v>-0.47776940467219298</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
+        <v>-0.33132378799296658</v>
       </c>
       <c r="G45" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
         <v>BAJO</v>
       </c>
       <c r="H45">
         <v>2.62</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>151501</v>
       </c>
@@ -2389,22 +2488,22 @@
         <v>117.72727272727273</v>
       </c>
       <c r="E46" s="4">
-        <f ca="1"/>
-        <v>65</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
+        <v>84.5</v>
       </c>
       <c r="F46" s="6">
-        <f ca="1"/>
-        <v>-0.44787644787644787</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
+        <v>-0.28223938223938227</v>
       </c>
       <c r="G46" s="7" t="str">
-        <f ca="1"/>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
         <v>BAJO</v>
       </c>
       <c r="H46">
         <v>2.62</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>151502</v>
       </c>
@@ -2418,22 +2517,22 @@
         <v>41.363636363636367</v>
       </c>
       <c r="E47" s="4">
-        <f ca="1"/>
-        <v>25.5</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
+        <v>51.833333333333336</v>
       </c>
       <c r="F47" s="5">
-        <f ca="1"/>
-        <v>-0.3835164835164836</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
+        <v>0.2531135531135531</v>
       </c>
       <c r="G47" s="7" t="str">
-        <f ca="1"/>
-        <v>BAJO</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H47">
         <v>2.62</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>151503</v>
       </c>
@@ -2447,16 +2546,16 @@
         <v>50.090909090909093</v>
       </c>
       <c r="E48" s="4">
-        <f ca="1"/>
-        <v>34</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
+        <v>53.833333333333336</v>
       </c>
       <c r="F48" s="6">
-        <f ca="1"/>
-        <v>-0.32123411978221417</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
+        <v>7.4712643678160884E-2</v>
       </c>
       <c r="G48" s="7" t="str">
-        <f ca="1"/>
-        <v>BAJO</v>
+        <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>
+        <v>SUBIÓ</v>
       </c>
       <c r="H48">
         <v>2.62</v>
@@ -2473,9 +2572,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -2483,7 +2582,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>

--- a/data/Comparación de Venta Diaria por SKU.xlsx
+++ b/data/Comparación de Venta Diaria por SKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D94364-479A-45E7-A3EB-F1618C20256A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1E24E8-FB47-44B8-826F-C9ADED3E019C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,7 +422,10 @@
       <sheetName val="INVENTARIO NACIONAL 05-10-26"/>
       <sheetName val="INVENTARIO NACIONAL 06-10-26"/>
       <sheetName val="INVENTARIO NACIONAL 07-10-26"/>
-      <sheetName val="INVENTARIO NACIONAL 08-10-2 "/>
+      <sheetName val="INVENTARIO NACIONAL 08-10-2 (2)"/>
+      <sheetName val="INVENTARIO NACIONAL 09-10-26 "/>
+      <sheetName val="INVENTARIO NACIONAL 13-10-26"/>
+      <sheetName val="INVENTARIO NACIONAL 30-10-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU SEPTIEMBRE"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -438,24 +441,27 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9">
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12">
         <row r="4">
           <cell r="F4">
-            <v>1170.5</v>
+            <v>1368.25</v>
           </cell>
           <cell r="G4">
-            <v>-3.3044196612969867E-2</v>
+            <v>0.13031805039239974</v>
           </cell>
           <cell r="H4" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="5">
           <cell r="F5">
-            <v>8.3333333333333339</v>
+            <v>5.35</v>
           </cell>
           <cell r="G5">
-            <v>-0.80722046968103744</v>
+            <v>-0.87623554153522609</v>
           </cell>
           <cell r="H5" t="str">
             <v>BAJO</v>
@@ -463,43 +469,43 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>491</v>
+            <v>553.29999999999995</v>
           </cell>
           <cell r="G6">
-            <v>-8.1718850426958367E-3</v>
+            <v>0.11767514461481943</v>
           </cell>
           <cell r="H6" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="7">
           <cell r="F7">
-            <v>88.5</v>
+            <v>112.1</v>
           </cell>
           <cell r="G7">
-            <v>-0.19810543657331137</v>
+            <v>1.5733113673805477E-2</v>
           </cell>
           <cell r="H7" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>11.166666666666666</v>
+            <v>16.3</v>
           </cell>
           <cell r="G8">
-            <v>-0.26004016064257041</v>
+            <v>8.0120481927710818E-2</v>
           </cell>
           <cell r="H8" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1524</v>
+            <v>1635.9</v>
           </cell>
           <cell r="G9">
-            <v>7.7377892030848328E-2</v>
+            <v>0.15648457583547559</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -507,21 +513,21 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>159.66666666666666</v>
+            <v>143.85</v>
           </cell>
           <cell r="G10">
-            <v>5.5171723240212245E-2</v>
+            <v>-4.9354160408531134E-2</v>
           </cell>
           <cell r="H10" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="11">
           <cell r="F11">
-            <v>408.83333333333331</v>
+            <v>420.55</v>
           </cell>
           <cell r="G11">
-            <v>0.22722517851457669</v>
+            <v>0.26239596124982945</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -529,10 +535,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>823.16666666666663</v>
+            <v>877.25</v>
           </cell>
           <cell r="G12">
-            <v>1.0076784353096446E-2</v>
+            <v>7.644040381504813E-2</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -540,10 +546,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>369.5</v>
+            <v>397.5</v>
           </cell>
           <cell r="G13">
-            <v>-7.9179882193022189E-2</v>
+            <v>-9.4019030357951339E-3</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -551,10 +557,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3576.5</v>
+            <v>3721.65</v>
           </cell>
           <cell r="G14">
-            <v>3.928198761045576E-2</v>
+            <v>8.1460592531931386E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -562,32 +568,32 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2157.1666666666665</v>
+            <v>2285.75</v>
           </cell>
           <cell r="G15">
-            <v>-2.3824038454802743E-3</v>
+            <v>5.7083096844716241E-2</v>
           </cell>
           <cell r="H15" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2114.6666666666665</v>
+            <v>2281.5500000000002</v>
           </cell>
           <cell r="G16">
-            <v>-2.6335433191715052E-2</v>
+            <v>5.0503338146962173E-2</v>
           </cell>
           <cell r="H16" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2682.8333333333335</v>
+            <v>2844.8</v>
           </cell>
           <cell r="G17">
-            <v>4.9946931385402848E-3</v>
+            <v>6.5667728038958595E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -595,10 +601,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>796</v>
+            <v>806.2</v>
           </cell>
           <cell r="G18">
-            <v>9.027518366330467E-2</v>
+            <v>0.10424604656954295</v>
           </cell>
           <cell r="H18" t="str">
             <v>SUBIÓ</v>
@@ -606,10 +612,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>1054.1666666666667</v>
+            <v>1044.5</v>
           </cell>
           <cell r="G19">
-            <v>0.20488708783596588</v>
+            <v>0.19383832086450536</v>
           </cell>
           <cell r="H19" t="str">
             <v>SUBIÓ</v>
@@ -617,10 +623,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>1017.6666666666666</v>
+            <v>1017.25</v>
           </cell>
           <cell r="G20">
-            <v>0.16863277308000124</v>
+            <v>0.16815429585551711</v>
           </cell>
           <cell r="H20" t="str">
             <v>SUBIÓ</v>
@@ -628,65 +634,65 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>279</v>
+            <v>311.8</v>
           </cell>
           <cell r="G21">
-            <v>-1.6503765422207994E-2</v>
+            <v>9.9118730972600488E-2</v>
           </cell>
           <cell r="H21" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>135.66666666666666</v>
+            <v>159.69999999999999</v>
           </cell>
           <cell r="G22">
-            <v>-5.2787474875700902E-2</v>
+            <v>0.11501110758489363</v>
           </cell>
           <cell r="H22" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="23">
           <cell r="F23">
-            <v>510.16666666666669</v>
+            <v>560.4</v>
           </cell>
           <cell r="G23">
-            <v>-2.850630427883083E-2</v>
+            <v>6.7151389249545446E-2</v>
           </cell>
           <cell r="H23" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="24">
           <cell r="F24">
-            <v>861.66666666666663</v>
+            <v>928.95</v>
           </cell>
           <cell r="G24">
-            <v>-3.9147110007265118E-2</v>
+            <v>3.5881190126210161E-2</v>
           </cell>
           <cell r="H24" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="25">
           <cell r="F25">
-            <v>43.333333333333336</v>
+            <v>68.75</v>
           </cell>
           <cell r="G25">
-            <v>-0.33796296296296291</v>
+            <v>5.0347222222222321E-2</v>
           </cell>
           <cell r="H25" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="26">
           <cell r="F26">
-            <v>623.5</v>
+            <v>713.4</v>
           </cell>
           <cell r="G26">
-            <v>-0.12979762735519884</v>
+            <v>-4.3265875785066799E-3</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -694,21 +700,21 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>1032.5</v>
+            <v>1173.3499999999999</v>
           </cell>
           <cell r="G27">
-            <v>-6.6915872494249018E-2</v>
+            <v>6.0372165626026986E-2</v>
           </cell>
           <cell r="H27" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="28">
           <cell r="F28">
-            <v>594.33333333333337</v>
+            <v>648.35</v>
           </cell>
           <cell r="G28">
-            <v>1.9360203736909165E-2</v>
+            <v>0.11200592500194917</v>
           </cell>
           <cell r="H28" t="str">
             <v>SUBIÓ</v>
@@ -716,10 +722,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>490.66666666666669</v>
+            <v>521.9</v>
           </cell>
           <cell r="G29">
-            <v>3.5459632294164711E-2</v>
+            <v>0.10137170263788953</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -727,10 +733,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>276.83333333333331</v>
+            <v>363.35</v>
           </cell>
           <cell r="G30">
-            <v>9.5777857742593175E-2</v>
+            <v>0.43823317740194323</v>
           </cell>
           <cell r="H30" t="str">
             <v>SUBIÓ</v>
@@ -738,21 +744,21 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>299.33333333333331</v>
+            <v>409.25</v>
           </cell>
           <cell r="G31">
-            <v>-3.0713374546168182E-2</v>
+            <v>0.32521342360906691</v>
           </cell>
           <cell r="H31" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="32">
           <cell r="F32">
-            <v>103.66666666666667</v>
+            <v>135.25</v>
           </cell>
           <cell r="G32">
-            <v>-0.247553062795557</v>
+            <v>-1.8310788518640764E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -760,21 +766,21 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>124.83333333333333</v>
+            <v>157.5</v>
           </cell>
           <cell r="G33">
-            <v>-0.17995421518861354</v>
+            <v>3.4637205135861437E-2</v>
           </cell>
           <cell r="H33" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="34">
           <cell r="F34">
-            <v>845.16666666666663</v>
+            <v>831.9</v>
           </cell>
           <cell r="G34">
-            <v>2.841076696165179E-2</v>
+            <v>1.2267699115044106E-2</v>
           </cell>
           <cell r="H34" t="str">
             <v>SUBIÓ</v>
@@ -782,10 +788,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>598.66666666666663</v>
+            <v>617.45000000000005</v>
           </cell>
           <cell r="G35">
-            <v>-4.8018311046861939E-2</v>
+            <v>-1.8149620527647237E-2</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -793,10 +799,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>786.33333333333337</v>
+            <v>805.55</v>
           </cell>
           <cell r="G36">
-            <v>-5.0843117890193468E-2</v>
+            <v>-2.7647317019642403E-2</v>
           </cell>
           <cell r="H36" t="str">
             <v>BAJO</v>
@@ -804,21 +810,21 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>516.16666666666663</v>
+            <v>576.04999999999995</v>
           </cell>
           <cell r="G37">
-            <v>-6.8061824647791092E-2</v>
+            <v>4.0057447681575598E-2</v>
           </cell>
           <cell r="H37" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="38">
           <cell r="F38">
-            <v>3.5</v>
+            <v>3.3</v>
           </cell>
           <cell r="G38">
-            <v>-6.0975609756097504E-2</v>
+            <v>-0.11463414634146341</v>
           </cell>
           <cell r="H38" t="str">
             <v>BAJO</v>
@@ -826,10 +832,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>1.3333333333333333</v>
+            <v>0.9</v>
           </cell>
           <cell r="G39">
-            <v>1.6666666666666665</v>
+            <v>0.8</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -837,10 +843,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>37.333333333333336</v>
+            <v>121.85</v>
           </cell>
           <cell r="G40">
-            <v>-0.7005711508081176</v>
+            <v>-2.2712358731316162E-2</v>
           </cell>
           <cell r="H40" t="str">
             <v>BAJO</v>
@@ -848,32 +854,32 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>608.33333333333337</v>
+            <v>445.8</v>
           </cell>
           <cell r="G41">
-            <v>9.1489468657315332E-3</v>
+            <v>-0.26047353340370993</v>
           </cell>
           <cell r="H41" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="42">
           <cell r="F42">
-            <v>440.83333333333331</v>
+            <v>374.3</v>
           </cell>
           <cell r="G42">
-            <v>2.3138868375707666E-2</v>
+            <v>-0.13127967085135561</v>
           </cell>
           <cell r="H42" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="43">
           <cell r="F43">
-            <v>276.5</v>
+            <v>327.7</v>
           </cell>
           <cell r="G43">
-            <v>1.1520737327188613E-3</v>
+            <v>0.18653719552337056</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -881,21 +887,21 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>483.33333333333331</v>
+            <v>595.15</v>
           </cell>
           <cell r="G44">
-            <v>-5.1018890376320125E-2</v>
+            <v>0.16852298081213735</v>
           </cell>
           <cell r="H44" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="45">
           <cell r="F45">
-            <v>258.66666666666669</v>
+            <v>283.95</v>
           </cell>
           <cell r="G45">
-            <v>-0.1890171488290342</v>
+            <v>-0.10974775545104742</v>
           </cell>
           <cell r="H45" t="str">
             <v>BAJO</v>
@@ -903,21 +909,21 @@
         </row>
         <row r="46">
           <cell r="F46">
-            <v>270</v>
+            <v>315.95</v>
           </cell>
           <cell r="G46">
-            <v>-0.11197488413813728</v>
+            <v>3.9153834653909314E-2</v>
           </cell>
           <cell r="H46" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="47">
           <cell r="F47">
-            <v>40.333333333333336</v>
+            <v>59.75</v>
           </cell>
           <cell r="G47">
-            <v>-0.33132378799296658</v>
+            <v>-9.4197437829691699E-3</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -925,10 +931,10 @@
         </row>
         <row r="48">
           <cell r="F48">
-            <v>84.5</v>
+            <v>96.05</v>
           </cell>
           <cell r="G48">
-            <v>-0.28223938223938227</v>
+            <v>-0.18413127413127417</v>
           </cell>
           <cell r="H48" t="str">
             <v>BAJO</v>
@@ -936,10 +942,10 @@
         </row>
         <row r="49">
           <cell r="F49">
-            <v>51.833333333333336</v>
+            <v>79.349999999999994</v>
           </cell>
           <cell r="G49">
-            <v>0.2531135531135531</v>
+            <v>0.91835164835164806</v>
           </cell>
           <cell r="H49" t="str">
             <v>SUBIÓ</v>
@@ -947,10 +953,10 @@
         </row>
         <row r="50">
           <cell r="F50">
-            <v>53.833333333333336</v>
+            <v>65.55</v>
           </cell>
           <cell r="G50">
-            <v>7.4712643678160884E-2</v>
+            <v>0.3086206896551722</v>
           </cell>
           <cell r="H50" t="str">
             <v>SUBIÓ</v>
@@ -1213,15 +1219,15 @@
       </c>
       <c r="E2" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1170.5</v>
+        <v>1368.25</v>
       </c>
       <c r="F2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>-3.3044196612969867E-2</v>
+        <v>0.13031805039239974</v>
       </c>
       <c r="G2" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H2">
         <v>1.36</v>
@@ -1242,11 +1248,11 @@
       </c>
       <c r="E3" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>8.3333333333333339</v>
+        <v>5.35</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.80722046968103744</v>
+        <v>-0.87623554153522609</v>
       </c>
       <c r="G3" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1271,15 +1277,15 @@
       </c>
       <c r="E4" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>491</v>
+        <v>553.29999999999995</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-8.1718850426958367E-3</v>
+        <v>0.11767514461481943</v>
       </c>
       <c r="G4" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H4">
         <v>2.0299999999999998</v>
@@ -1300,15 +1306,15 @@
       </c>
       <c r="E5" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>88.5</v>
+        <v>112.1</v>
       </c>
       <c r="F5" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-0.19810543657331137</v>
+        <v>1.5733113673805477E-2</v>
       </c>
       <c r="G5" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1329,15 +1335,15 @@
       </c>
       <c r="E6" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>11.166666666666666</v>
+        <v>16.3</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.26004016064257041</v>
+        <v>8.0120481927710818E-2</v>
       </c>
       <c r="G6" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H6">
         <v>8.7799999999999994</v>
@@ -1358,11 +1364,11 @@
       </c>
       <c r="E7" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1524</v>
+        <v>1635.9</v>
       </c>
       <c r="F7" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>7.7377892030848328E-2</v>
+        <v>0.15648457583547559</v>
       </c>
       <c r="G7" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1387,15 +1393,15 @@
       </c>
       <c r="E8" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>159.66666666666666</v>
+        <v>143.85</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>5.5171723240212245E-2</v>
+        <v>-4.9354160408531134E-2</v>
       </c>
       <c r="G8" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H8">
         <v>0.63</v>
@@ -1416,11 +1422,11 @@
       </c>
       <c r="E9" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>408.83333333333331</v>
+        <v>420.55</v>
       </c>
       <c r="F9" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>0.22722517851457669</v>
+        <v>0.26239596124982945</v>
       </c>
       <c r="G9" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1445,11 +1451,11 @@
       </c>
       <c r="E10" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>823.16666666666663</v>
+        <v>877.25</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>1.0076784353096446E-2</v>
+        <v>7.644040381504813E-2</v>
       </c>
       <c r="G10" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1474,11 +1480,11 @@
       </c>
       <c r="E11" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>369.5</v>
+        <v>397.5</v>
       </c>
       <c r="F11" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-7.9179882193022189E-2</v>
+        <v>-9.4019030357951339E-3</v>
       </c>
       <c r="G11" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1503,11 +1509,11 @@
       </c>
       <c r="E12" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3576.5</v>
+        <v>3721.65</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>3.928198761045576E-2</v>
+        <v>8.1460592531931386E-2</v>
       </c>
       <c r="G12" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1532,15 +1538,15 @@
       </c>
       <c r="E13" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2157.1666666666665</v>
+        <v>2285.75</v>
       </c>
       <c r="F13" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-2.3824038454802743E-3</v>
+        <v>5.7083096844716241E-2</v>
       </c>
       <c r="G13" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H13">
         <v>1.1599999999999999</v>
@@ -1561,15 +1567,15 @@
       </c>
       <c r="E14" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2114.6666666666665</v>
+        <v>2281.5500000000002</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-2.6335433191715052E-2</v>
+        <v>5.0503338146962173E-2</v>
       </c>
       <c r="G14" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H14">
         <v>1.1599999999999999</v>
@@ -1590,11 +1596,11 @@
       </c>
       <c r="E15" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2682.8333333333335</v>
+        <v>2844.8</v>
       </c>
       <c r="F15" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>4.9946931385402848E-3</v>
+        <v>6.5667728038958595E-2</v>
       </c>
       <c r="G15" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1619,11 +1625,11 @@
       </c>
       <c r="E16" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>796</v>
+        <v>806.2</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>9.027518366330467E-2</v>
+        <v>0.10424604656954295</v>
       </c>
       <c r="G16" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1648,11 +1654,11 @@
       </c>
       <c r="E17" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>1054.1666666666667</v>
+        <v>1044.5</v>
       </c>
       <c r="F17" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>0.20488708783596588</v>
+        <v>0.19383832086450536</v>
       </c>
       <c r="G17" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1677,11 +1683,11 @@
       </c>
       <c r="E18" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>1017.6666666666666</v>
+        <v>1017.25</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>0.16863277308000124</v>
+        <v>0.16815429585551711</v>
       </c>
       <c r="G18" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1706,15 +1712,15 @@
       </c>
       <c r="E19" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>279</v>
+        <v>311.8</v>
       </c>
       <c r="F19" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-1.6503765422207994E-2</v>
+        <v>9.9118730972600488E-2</v>
       </c>
       <c r="G19" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H19">
         <v>3.68</v>
@@ -1735,15 +1741,15 @@
       </c>
       <c r="E20" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>135.66666666666666</v>
+        <v>159.69999999999999</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-5.2787474875700902E-2</v>
+        <v>0.11501110758489363</v>
       </c>
       <c r="G20" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H20">
         <v>3.68</v>
@@ -1764,15 +1770,15 @@
       </c>
       <c r="E21" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F23</f>
-        <v>510.16666666666669</v>
+        <v>560.4</v>
       </c>
       <c r="F21" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G23</f>
-        <v>-2.850630427883083E-2</v>
+        <v>6.7151389249545446E-2</v>
       </c>
       <c r="G21" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H23</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H21">
         <v>4.1500000000000004</v>
@@ -1793,15 +1799,15 @@
       </c>
       <c r="E22" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>861.66666666666663</v>
+        <v>928.95</v>
       </c>
       <c r="F22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>-3.9147110007265118E-2</v>
+        <v>3.5881190126210161E-2</v>
       </c>
       <c r="G22" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
@@ -1822,15 +1828,15 @@
       </c>
       <c r="E23" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>43.333333333333336</v>
+        <v>68.75</v>
       </c>
       <c r="F23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.33796296296296291</v>
+        <v>5.0347222222222321E-2</v>
       </c>
       <c r="G23" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H23">
         <v>4.1500000000000004</v>
@@ -1851,11 +1857,11 @@
       </c>
       <c r="E24" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>623.5</v>
+        <v>713.4</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.12979762735519884</v>
+        <v>-4.3265875785066799E-3</v>
       </c>
       <c r="G24" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1880,15 +1886,15 @@
       </c>
       <c r="E25" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>1032.5</v>
+        <v>1173.3499999999999</v>
       </c>
       <c r="F25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-6.6915872494249018E-2</v>
+        <v>6.0372165626026986E-2</v>
       </c>
       <c r="G25" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H25">
         <v>1.63</v>
@@ -1909,11 +1915,11 @@
       </c>
       <c r="E26" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>594.33333333333337</v>
+        <v>648.35</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>1.9360203736909165E-2</v>
+        <v>0.11200592500194917</v>
       </c>
       <c r="G26" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1938,11 +1944,11 @@
       </c>
       <c r="E27" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>490.66666666666669</v>
+        <v>521.9</v>
       </c>
       <c r="F27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>3.5459632294164711E-2</v>
+        <v>0.10137170263788953</v>
       </c>
       <c r="G27" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1967,11 +1973,11 @@
       </c>
       <c r="E28" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>276.83333333333331</v>
+        <v>363.35</v>
       </c>
       <c r="F28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>9.5777857742593175E-2</v>
+        <v>0.43823317740194323</v>
       </c>
       <c r="G28" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1996,15 +2002,15 @@
       </c>
       <c r="E29" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>299.33333333333331</v>
+        <v>409.25</v>
       </c>
       <c r="F29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-3.0713374546168182E-2</v>
+        <v>0.32521342360906691</v>
       </c>
       <c r="G29" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H29">
         <v>1.63</v>
@@ -2025,11 +2031,11 @@
       </c>
       <c r="E30" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>103.66666666666667</v>
+        <v>135.25</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.247553062795557</v>
+        <v>-1.8310788518640764E-2</v>
       </c>
       <c r="G30" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -2054,15 +2060,15 @@
       </c>
       <c r="E31" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>124.83333333333333</v>
+        <v>157.5</v>
       </c>
       <c r="F31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.17995421518861354</v>
+        <v>3.4637205135861437E-2</v>
       </c>
       <c r="G31" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H31">
         <v>6.15</v>
@@ -2083,11 +2089,11 @@
       </c>
       <c r="E32" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>845.16666666666663</v>
+        <v>831.9</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>2.841076696165179E-2</v>
+        <v>1.2267699115044106E-2</v>
       </c>
       <c r="G32" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2112,11 +2118,11 @@
       </c>
       <c r="E33" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>598.66666666666663</v>
+        <v>617.45000000000005</v>
       </c>
       <c r="F33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-4.8018311046861939E-2</v>
+        <v>-1.8149620527647237E-2</v>
       </c>
       <c r="G33" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2141,11 +2147,11 @@
       </c>
       <c r="E34" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>786.33333333333337</v>
+        <v>805.55</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>-5.0843117890193468E-2</v>
+        <v>-2.7647317019642403E-2</v>
       </c>
       <c r="G34" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2170,15 +2176,15 @@
       </c>
       <c r="E35" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>516.16666666666663</v>
+        <v>576.04999999999995</v>
       </c>
       <c r="F35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-6.8061824647791092E-2</v>
+        <v>4.0057447681575598E-2</v>
       </c>
       <c r="G35" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H35">
         <v>1.1599999999999999</v>
@@ -2199,11 +2205,11 @@
       </c>
       <c r="E36" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-6.0975609756097504E-2</v>
+        <v>-0.11463414634146341</v>
       </c>
       <c r="G36" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2228,11 +2234,11 @@
       </c>
       <c r="E37" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>1.3333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="F37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>1.6666666666666665</v>
+        <v>0.8</v>
       </c>
       <c r="G37" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2257,11 +2263,11 @@
       </c>
       <c r="E38" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>37.333333333333336</v>
+        <v>121.85</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>-0.7005711508081176</v>
+        <v>-2.2712358731316162E-2</v>
       </c>
       <c r="G38" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2286,15 +2292,15 @@
       </c>
       <c r="E39" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>608.33333333333337</v>
+        <v>445.8</v>
       </c>
       <c r="F39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>9.1489468657315332E-3</v>
+        <v>-0.26047353340370993</v>
       </c>
       <c r="G39" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H39">
         <v>1.1599999999999999</v>
@@ -2315,15 +2321,15 @@
       </c>
       <c r="E40" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>440.83333333333331</v>
+        <v>374.3</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>2.3138868375707666E-2</v>
+        <v>-0.13127967085135561</v>
       </c>
       <c r="G40" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H40">
         <v>1.1599999999999999</v>
@@ -2344,11 +2350,11 @@
       </c>
       <c r="E41" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>276.5</v>
+        <v>327.7</v>
       </c>
       <c r="F41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>1.1520737327188613E-3</v>
+        <v>0.18653719552337056</v>
       </c>
       <c r="G41" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2373,15 +2379,15 @@
       </c>
       <c r="E42" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>483.33333333333331</v>
+        <v>595.15</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>-5.1018890376320125E-2</v>
+        <v>0.16852298081213735</v>
       </c>
       <c r="G42" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H42">
         <v>0.81</v>
@@ -2402,11 +2408,11 @@
       </c>
       <c r="E43" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>258.66666666666669</v>
+        <v>283.95</v>
       </c>
       <c r="F43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.1890171488290342</v>
+        <v>-0.10974775545104742</v>
       </c>
       <c r="G43" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2431,15 +2437,15 @@
       </c>
       <c r="E44" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F46</f>
-        <v>270</v>
+        <v>315.95</v>
       </c>
       <c r="F44" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G46</f>
-        <v>-0.11197488413813728</v>
+        <v>3.9153834653909314E-2</v>
       </c>
       <c r="G44" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H46</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H44">
         <v>0.81</v>
@@ -2460,11 +2466,11 @@
       </c>
       <c r="E45" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>40.333333333333336</v>
+        <v>59.75</v>
       </c>
       <c r="F45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.33132378799296658</v>
+        <v>-9.4197437829691699E-3</v>
       </c>
       <c r="G45" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
@@ -2489,11 +2495,11 @@
       </c>
       <c r="E46" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F48</f>
-        <v>84.5</v>
+        <v>96.05</v>
       </c>
       <c r="F46" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G48</f>
-        <v>-0.28223938223938227</v>
+        <v>-0.18413127413127417</v>
       </c>
       <c r="G46" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H48</f>
@@ -2518,11 +2524,11 @@
       </c>
       <c r="E47" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F49</f>
-        <v>51.833333333333336</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="F47" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!G49</f>
-        <v>0.2531135531135531</v>
+        <v>0.91835164835164806</v>
       </c>
       <c r="G47" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H49</f>
@@ -2547,11 +2553,11 @@
       </c>
       <c r="E48" s="4">
         <f ca="1">'[1]DESV. VTS BY SKU'!F50</f>
-        <v>53.833333333333336</v>
+        <v>65.55</v>
       </c>
       <c r="F48" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G50</f>
-        <v>7.4712643678160884E-2</v>
+        <v>0.3086206896551722</v>
       </c>
       <c r="G48" s="7" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H50</f>
